--- a/Models/CLIP/male1data/clip_big5_male1_cropped.xlsx
+++ b/Models/CLIP/male1data/clip_big5_male1_cropped.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/yq_c_tamu_edu/Documents/Research/genderBias/GenderBias-SRL-Implementation/Models/CLIP/male1data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A645F574EF189EEBA4C46DBFEB9D53E2792CEEAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141C65EA-3BDF-44F7-9A6F-2BF5F2D5123F}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extraversion" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,25 @@
     <sheet name="Neuroticism" sheetId="4" r:id="rId4"/>
     <sheet name="Openness" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Positive Trait</t>
   </si>
@@ -159,14 +178,25 @@
   </si>
   <si>
     <t>Likes to reflect, play with ideas</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -194,21 +224,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +285,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -280,6 +319,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -314,9 +354,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,11 +530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,62 +548,62 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.08238936215639114</v>
+        <v>8.2389362156391144E-2</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0.004627461079508066</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>4.6274610795080662E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.0278451144695282</v>
+        <v>2.7845114469528202E-2</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>0.001532973139546812</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.532973139546812E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.0273618046194315</v>
+        <v>2.7361804619431499E-2</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.001391595927998424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.391595927998424E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.005872710607945919</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>5.872710607945919E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.005184853915125132</v>
+        <v>5.1848539151251316E-3</v>
       </c>
     </row>
   </sheetData>
@@ -571,11 +612,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,68 +630,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.0276912022382021</v>
+        <v>2.7691202238202099E-2</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>0.005369279999285936</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>5.3692799992859364E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.01204795204102993</v>
+        <v>1.204795204102993E-2</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>0.004924901761114597</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>4.9249017611145973E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.007770675700157881</v>
+        <v>7.7706757001578808E-3</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0.003316401736810803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.316401736810803E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.003370999125763774</v>
+        <v>3.3709991257637739E-3</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>0.002246507909148932</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>2.2465079091489319E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.002393640344962478</v>
+        <v>2.3936403449624781E-3</v>
       </c>
     </row>
   </sheetData>
@@ -659,11 +700,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,68 +718,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.05131963267922401</v>
+        <v>5.1319632679224007E-2</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.002532541286200285</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2.532541286200285E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.01098974328488111</v>
+        <v>1.098974328488111E-2</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.002080138539895415</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2.0801385398954149E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0.008207108825445175</v>
+        <v>8.2071088254451752E-3</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>0.001280121738091111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.280121738091111E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
-        <v>0.002173021202906966</v>
+        <v>2.1730212029069662E-3</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>0.0002614160184748471</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>2.6141601847484708E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
-        <v>0.00143316516187042</v>
+        <v>1.43316516187042E-3</v>
       </c>
     </row>
   </sheetData>
@@ -747,11 +788,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -765,62 +806,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2">
-        <v>0.06982965022325516</v>
+        <v>6.9829650223255157E-2</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0.01230957172811031</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.230957172811031E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0.04691414907574654</v>
+        <v>4.6914149075746543E-2</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0.01081841345876455</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.081841345876455E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
-        <v>0.01722707785665989</v>
+        <v>1.7227077856659889E-2</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>0.005760243162512779</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>5.7602431625127792E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>0.003252281807363033</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.2522818073630329E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>0.003189449664205313</v>
+        <v>3.1894496642053132E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>4.4656959051887192E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>7.0659919641911971E-3</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +883,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,12 +901,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
       <c r="B2">
-        <v>0.1595276445150375</v>
+        <v>0.15952764451503751</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
@@ -861,7 +915,7 @@
         <v>0.1970888078212738</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -872,47 +926,47 @@
         <v>46</v>
       </c>
       <c r="D3">
-        <v>0.01800475269556046</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.8004752695560459E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>0.01088425144553185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.088425144553185E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5">
-        <v>0.01023132354021072</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1.023132354021072E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6">
-        <v>0.007760633248835802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>7.7606332488358021E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7">
-        <v>0.002175928791984916</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>2.1759287919849162E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8">
-        <v>0.001166894333437085</v>
+        <v>1.1668943334370849E-3</v>
       </c>
     </row>
   </sheetData>
